--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A684B457-5731-4E88-8D33-A93E35FB3194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1458E0DB-FB82-4164-935B-A6891BC158E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{7048E13E-4362-4462-A19B-6BDE3C722A3C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{0B2176BE-A407-4AFE-96C0-576021C38A0D}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
   <si>
     <r>
       <t>ICT</t>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2024</t>
+      <t>2025</t>
     </r>
     <r>
       <rPr>
@@ -465,8 +465,11 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>対応している</t>
-    </r>
+      <t>評価不要</t>
+    </r>
+    <rPh sb="0" eb="4">
+      <t>ヒョウカフヨウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -478,20 +481,26 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>米国リハビリテーション法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>508</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>聴力なしでの使用（全ろう）</t>
+      <t>条を用いているため評価の対象外である。</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -504,7 +513,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
+      <t>製品・サービスが視覚的な操作モードで提供される場合、色知覚を必要としない操作モードが用意されているか</t>
     </r>
   </si>
   <si>
@@ -517,7 +526,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた聴力での使用（難聴）</t>
+      <t>聴力なしでの使用（全ろう）</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -530,7 +539,7 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+      <t>製品・サービスが聴覚的な操作モードで提供される場合、聴力を必要としない操作モードが用意されているか</t>
     </r>
   </si>
   <si>
@@ -543,7 +552,46 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>限られた聴力での使用（難聴）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>製品・サービスが聴覚的な操作モードで行われる場合、強化された音声機能によって限られた聴力を補う操作モードが提供されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>発話能力なしでの使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2551,7 +2599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D80E66D6-7020-4A06-832A-5DBC7DEDCD9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAA1F34-468B-42E9-B8B2-3B501B8DADE6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2853,7 +2901,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>25</v>
       </c>
@@ -2862,30 +2910,30 @@
       <c r="D22" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="E22" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="38"/>
+      <c r="E22" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="44"/>
-      <c r="G23" s="44"/>
-      <c r="H23" s="44"/>
-      <c r="I23" s="45"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="42"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="32" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B24" s="33"/>
       <c r="C24" s="34"/>
@@ -2902,7 +2950,7 @@
     </row>
     <row r="25" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="39" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B25" s="40"/>
       <c r="C25" s="41"/>
@@ -2915,7 +2963,7 @@
     </row>
     <row r="26" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="32" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="34"/>
@@ -2932,7 +2980,7 @@
     </row>
     <row r="27" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="39" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
@@ -2945,12 +2993,12 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="33"/>
       <c r="C28" s="34"/>
       <c r="D28" s="46" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>21</v>
@@ -2962,7 +3010,7 @@
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
@@ -2975,7 +3023,7 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -2992,7 +3040,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3005,7 +3053,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3018,7 +3066,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3031,15 +3079,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3048,7 +3096,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3089,15 +3137,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3106,7 +3154,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3130,7 +3178,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3160,15 +3208,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3177,7 +3225,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3201,10 +3249,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3227,7 +3275,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3367,7 +3415,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{E12DB3D7-7132-4CA6-9081-F1910943B59A}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{FB3DC6A5-3633-4C98-AB54-BD2268167EAA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3375,7 +3423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{665B1608-36F1-42A4-847E-510AAC416EE9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E5912-C0E4-48CC-B2F8-A19257794A72}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3388,43 +3436,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3432,36 +3480,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3469,10 +3517,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3490,14 +3538,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3513,15 +3561,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3536,15 +3584,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3559,17 +3607,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3582,10 +3630,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3593,7 +3641,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3605,10 +3653,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3617,7 +3665,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3628,10 +3676,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3641,10 +3689,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3653,10 +3701,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3666,10 +3714,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3678,10 +3726,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3699,17 +3747,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3724,10 +3772,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3745,10 +3793,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3763,17 +3811,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3786,17 +3834,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3809,20 +3857,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3834,20 +3882,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3859,17 +3907,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3885,10 +3933,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3896,7 +3944,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3905,23 +3953,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3930,23 +3978,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -3958,15 +4006,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -3981,15 +4029,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4004,27 +4052,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4033,10 +4081,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4054,29 +4102,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4085,10 +4133,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4106,17 +4154,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4131,10 +4179,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4152,30 +4200,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4183,10 +4231,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4204,31 +4252,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4237,10 +4285,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4258,15 +4306,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4281,14 +4329,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4304,10 +4352,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4317,10 +4365,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4329,27 +4377,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4358,10 +4406,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4371,10 +4419,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4383,14 +4431,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4406,10 +4454,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4419,10 +4467,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4431,10 +4479,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4444,10 +4492,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4456,10 +4504,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4477,10 +4525,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4498,10 +4546,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4519,14 +4567,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4542,10 +4590,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4563,15 +4611,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4586,10 +4634,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4607,20 +4655,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4632,10 +4680,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4653,29 +4701,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4684,10 +4732,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4705,10 +4753,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4716,7 +4764,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4728,10 +4776,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4739,7 +4787,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4751,10 +4799,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4762,7 +4810,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4774,10 +4822,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4795,24 +4843,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4824,17 +4872,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4847,20 +4895,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4872,10 +4920,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4893,14 +4941,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4916,10 +4964,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4937,22 +4985,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -4964,10 +5012,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -4985,31 +5033,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5018,10 +5066,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5039,29 +5087,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5070,14 +5118,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5085,10 +5133,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5097,43 +5145,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5143,22 +5191,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5168,22 +5216,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5193,32 +5241,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5227,23 +5275,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5252,26 +5300,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5279,23 +5327,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5307,31 +5355,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5340,10 +5388,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5361,15 +5409,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5384,14 +5432,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5399,10 +5447,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5411,22 +5459,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5438,24 +5486,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5467,10 +5515,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5488,24 +5536,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5514,25 +5562,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5541,20 +5589,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5569,24 +5617,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5598,24 +5646,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1458E0DB-FB82-4164-935B-A6891BC158E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EFC108D-FF83-4FEB-AFD7-8032849B3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{0B2176BE-A407-4AFE-96C0-576021C38A0D}"/>
+    <workbookView xWindow="1140" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{384D8F9E-4E71-4DDD-A953-15B4EDE49C93}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2025</t>
+      <t>2024</t>
     </r>
     <r>
       <rPr>
@@ -2599,7 +2599,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BAA1F34-468B-42E9-B8B2-3B501B8DADE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0337A79-7B4A-4863-8893-0A7C9453C307}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3415,7 +3415,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{FB3DC6A5-3633-4C98-AB54-BD2268167EAA}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{652103AE-AEAC-4AA7-A90A-D4CB02E98205}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3423,7 +3423,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C72E5912-C0E4-48CC-B2F8-A19257794A72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18736D80-00F9-4E74-BE24-89901731352D}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EFC108D-FF83-4FEB-AFD7-8032849B3551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE2EF9B-D880-4828-96BF-6BC2894FD664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{384D8F9E-4E71-4DDD-A953-15B4EDE49C93}"/>
+    <workbookView xWindow="2660" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{0C676DF9-F0DB-49D1-BDB4-25666544DF64}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="235">
   <si>
     <r>
       <t>ICT</t>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2024</t>
+      <t>2025</t>
     </r>
     <r>
       <rPr>
@@ -593,6 +593,9 @@
       </rPr>
       <t>対応している</t>
     </r>
+    <rPh sb="0" eb="2">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
   <si>
@@ -604,72 +607,98 @@
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>すべての製品において要件を満たす。</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた器用さ又は力での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが発話による操作モードで行われる場合、音声入力を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた器用さ又は力での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>限られた手の届く範囲での使用</t>
-    </r>
-    <phoneticPr fontId="4"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
+      <t>製品・サービスが手の動作を必要とする場合、細かい運動制御等を必要としない操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
-      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
+      <t>限られた手の届く範囲での使用</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <sz val="10.5"/>
         <color rgb="FF000000"/>
         <rFont val="ＭＳ Ｐゴシック"/>
         <family val="3"/>
         <charset val="128"/>
       </rPr>
+      <t>製品・サービスが手動による操作モードで提供される場合、手の届く範囲で、かつ限られた力で対応可能な操作モードが用意されているか</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
       <t>光の点滅による影響の最小化（光感受性発作）</t>
+    </r>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF000000"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>対応している</t>
     </r>
     <phoneticPr fontId="4"/>
   </si>
@@ -2599,7 +2628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0337A79-7B4A-4863-8893-0A7C9453C307}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A979893C-E8DE-439D-9E11-08A170BA34C6}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2901,7 +2930,7 @@
       <c r="H21" s="44"/>
       <c r="I21" s="45"/>
     </row>
-    <row r="22" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="32" t="s">
         <v>25</v>
       </c>
@@ -3000,30 +3029,30 @@
       <c r="D28" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="E28" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="37"/>
-      <c r="I28" s="38"/>
+      <c r="E28" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="42"/>
+      <c r="G28" s="42"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="42"/>
     </row>
     <row r="29" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="39" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B29" s="40"/>
       <c r="C29" s="41"/>
       <c r="D29" s="47"/>
-      <c r="E29" s="43"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="45"/>
+      <c r="E29" s="42"/>
+      <c r="F29" s="42"/>
+      <c r="G29" s="42"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="42"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B30" s="33"/>
       <c r="C30" s="34"/>
@@ -3040,7 +3069,7 @@
     </row>
     <row r="31" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="39" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B31" s="40"/>
       <c r="C31" s="41"/>
@@ -3053,7 +3082,7 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B32" s="33"/>
       <c r="C32" s="34"/>
@@ -3066,7 +3095,7 @@
     </row>
     <row r="33" spans="1:9" ht="69.650000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="39" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B33" s="40"/>
       <c r="C33" s="41"/>
@@ -3079,15 +3108,15 @@
     </row>
     <row r="34" spans="1:9" ht="25.75" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B34" s="33"/>
       <c r="C34" s="34"/>
       <c r="D34" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E34" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F34" s="42"/>
       <c r="G34" s="42"/>
@@ -3096,7 +3125,7 @@
     </row>
     <row r="35" spans="1:9" ht="51.65" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="39" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B35" s="40"/>
       <c r="C35" s="41"/>
@@ -3137,15 +3166,15 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="32" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B38" s="33"/>
       <c r="C38" s="34"/>
       <c r="D38" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E38" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F38" s="42"/>
       <c r="G38" s="42"/>
@@ -3154,7 +3183,7 @@
     </row>
     <row r="39" spans="1:9" ht="64.400000000000006" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="39" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B39" s="40"/>
       <c r="C39" s="41"/>
@@ -3178,7 +3207,7 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="26" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5"/>
@@ -3208,15 +3237,15 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="32" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B43" s="33"/>
       <c r="C43" s="34"/>
       <c r="D43" s="42" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="E43" s="42" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F43" s="42"/>
       <c r="G43" s="42"/>
@@ -3225,7 +3254,7 @@
     </row>
     <row r="44" spans="1:9" ht="52.4" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="39" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
@@ -3249,10 +3278,10 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="54" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B46" s="42" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C46" s="42"/>
       <c r="D46" s="42"/>
@@ -3275,7 +3304,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="54" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B48" s="42"/>
       <c r="C48" s="42"/>
@@ -3415,7 +3444,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{652103AE-AEAC-4AA7-A90A-D4CB02E98205}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{4CC28AF9-C221-4F11-8B9B-ADCE71E42F59}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3423,7 +3452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18736D80-00F9-4E74-BE24-89901731352D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614CED36-19BF-4F04-8083-5FCF41145834}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
@@ -3436,43 +3465,43 @@
   <sheetData>
     <row r="1" spans="1:13" ht="71.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="59" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="60" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="60" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="61" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="60" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="60" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="60" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="60" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="60" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J1" s="60" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K1" s="60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L1" s="60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M1" s="60" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3480,36 +3509,36 @@
         <v>301</v>
       </c>
       <c r="B2" s="63" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C2" s="64" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D2" s="65"/>
       <c r="E2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G2" s="67"/>
       <c r="H2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="I2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M2" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -3517,10 +3546,10 @@
         <v>302</v>
       </c>
       <c r="B3" s="63" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C3" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D3" s="65"/>
       <c r="E3" s="66"/>
@@ -3538,14 +3567,14 @@
         <v>302.10000000000002</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D4" s="65"/>
       <c r="E4" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" s="65"/>
       <c r="G4" s="68"/>
@@ -3561,15 +3590,15 @@
         <v>302.2</v>
       </c>
       <c r="B5" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C5" s="64" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
       <c r="F5" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G5" s="68"/>
       <c r="H5" s="65"/>
@@ -3584,15 +3613,15 @@
         <v>302.3</v>
       </c>
       <c r="B6" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C6" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D6" s="65"/>
       <c r="E6" s="65"/>
       <c r="F6" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G6" s="68"/>
       <c r="H6" s="65"/>
@@ -3607,17 +3636,17 @@
         <v>302.39999999999998</v>
       </c>
       <c r="B7" s="64" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C7" s="64" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D7" s="65"/>
       <c r="E7" s="65"/>
       <c r="F7" s="65"/>
       <c r="G7" s="68"/>
       <c r="H7" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I7" s="65"/>
       <c r="J7" s="65"/>
@@ -3630,10 +3659,10 @@
         <v>302.5</v>
       </c>
       <c r="B8" s="64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C8" s="64" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
@@ -3641,7 +3670,7 @@
       <c r="G8" s="68"/>
       <c r="H8" s="65"/>
       <c r="I8" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J8" s="65"/>
       <c r="K8" s="65"/>
@@ -3653,10 +3682,10 @@
         <v>302.60000000000002</v>
       </c>
       <c r="B9" s="64" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C9" s="64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D9" s="65"/>
       <c r="E9" s="65"/>
@@ -3665,7 +3694,7 @@
       <c r="H9" s="65"/>
       <c r="I9" s="65"/>
       <c r="J9" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K9" s="65"/>
       <c r="L9" s="65"/>
@@ -3676,10 +3705,10 @@
         <v>302.7</v>
       </c>
       <c r="B10" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C10" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
@@ -3689,10 +3718,10 @@
       <c r="I10" s="65"/>
       <c r="J10" s="65"/>
       <c r="K10" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L10" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M10" s="65"/>
     </row>
@@ -3701,10 +3730,10 @@
         <v>302.8</v>
       </c>
       <c r="B11" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C11" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="65"/>
       <c r="E11" s="65"/>
@@ -3714,10 +3743,10 @@
       <c r="I11" s="65"/>
       <c r="J11" s="65"/>
       <c r="K11" s="65" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L11" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M11" s="65"/>
     </row>
@@ -3726,10 +3755,10 @@
         <v>302.89999999999998</v>
       </c>
       <c r="B12" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C12" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D12" s="65"/>
       <c r="E12" s="65"/>
@@ -3747,17 +3776,17 @@
         <v>402</v>
       </c>
       <c r="B13" s="64" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C13" s="64" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D13" s="65"/>
       <c r="E13" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G13" s="67"/>
       <c r="H13" s="66"/>
@@ -3772,10 +3801,10 @@
         <v>402.1</v>
       </c>
       <c r="B14" s="70" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C14" s="70" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D14" s="71"/>
       <c r="E14" s="66"/>
@@ -3793,10 +3822,10 @@
         <v>402.2</v>
       </c>
       <c r="B15" s="64" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C15" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D15" s="65"/>
       <c r="E15" s="66"/>
@@ -3811,17 +3840,17 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="65" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" s="64" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C16" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D16" s="65"/>
       <c r="E16" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" s="65"/>
       <c r="G16" s="68"/>
@@ -3834,17 +3863,17 @@
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="65" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B17" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C17" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D17" s="65"/>
       <c r="E17" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F17" s="65"/>
       <c r="G17" s="68"/>
@@ -3857,20 +3886,20 @@
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="65" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B18" s="64" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C18" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D18" s="65"/>
       <c r="E18" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G18" s="68"/>
       <c r="H18" s="65"/>
@@ -3882,20 +3911,20 @@
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C19" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D19" s="65"/>
       <c r="E19" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F19" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G19" s="68"/>
       <c r="H19" s="65"/>
@@ -3907,17 +3936,17 @@
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="65" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C20" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D20" s="65"/>
       <c r="E20" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F20" s="65"/>
       <c r="G20" s="68"/>
@@ -3933,10 +3962,10 @@
         <v>402.3</v>
       </c>
       <c r="B21" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C21" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D21" s="65"/>
       <c r="E21" s="65"/>
@@ -3944,7 +3973,7 @@
       <c r="G21" s="68"/>
       <c r="H21" s="65"/>
       <c r="I21" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J21" s="65"/>
       <c r="K21" s="65"/>
@@ -3953,23 +3982,23 @@
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="65" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B22" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C22" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D22" s="65"/>
       <c r="E22" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F22" s="65"/>
       <c r="G22" s="68"/>
       <c r="H22" s="65"/>
       <c r="I22" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J22" s="65"/>
       <c r="K22" s="65"/>
@@ -3978,23 +4007,23 @@
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="65" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B23" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C23" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D23" s="65"/>
       <c r="E23" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" s="65"/>
       <c r="G23" s="68"/>
       <c r="H23" s="65"/>
       <c r="I23" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J23" s="65"/>
       <c r="K23" s="65"/>
@@ -4006,15 +4035,15 @@
         <v>402.4</v>
       </c>
       <c r="B24" s="64" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C24" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D24" s="65"/>
       <c r="E24" s="65"/>
       <c r="F24" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G24" s="68"/>
       <c r="H24" s="65"/>
@@ -4029,15 +4058,15 @@
         <v>402.5</v>
       </c>
       <c r="B25" s="64" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C25" s="64" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="D25" s="65"/>
       <c r="E25" s="65"/>
       <c r="F25" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G25" s="68"/>
       <c r="H25" s="65"/>
@@ -4052,27 +4081,27 @@
         <v>403</v>
       </c>
       <c r="B26" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C26" s="64" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D26" s="65"/>
       <c r="E26" s="66"/>
       <c r="F26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G26" s="67"/>
       <c r="H26" s="66"/>
       <c r="I26" s="66"/>
       <c r="J26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L26" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M26" s="66"/>
     </row>
@@ -4081,10 +4110,10 @@
         <v>403.1</v>
       </c>
       <c r="B27" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D27" s="65"/>
       <c r="E27" s="66"/>
@@ -4102,29 +4131,29 @@
         <v>404</v>
       </c>
       <c r="B28" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C28" s="64" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D28" s="65"/>
       <c r="E28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F28" s="66"/>
       <c r="G28" s="67"/>
       <c r="H28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J28" s="66"/>
       <c r="K28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L28" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M28" s="66"/>
     </row>
@@ -4133,10 +4162,10 @@
         <v>404.1</v>
       </c>
       <c r="B29" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D29" s="65"/>
       <c r="E29" s="66"/>
@@ -4154,17 +4183,17 @@
         <v>405</v>
       </c>
       <c r="B30" s="64" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C30" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D30" s="65"/>
       <c r="E30" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F30" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G30" s="67"/>
       <c r="H30" s="66"/>
@@ -4179,10 +4208,10 @@
         <v>405.1</v>
       </c>
       <c r="B31" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C31" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D31" s="65"/>
       <c r="E31" s="66"/>
@@ -4200,30 +4229,30 @@
         <v>406</v>
       </c>
       <c r="B32" s="64" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C32" s="64" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D32" s="65"/>
       <c r="E32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F32" s="66"/>
       <c r="G32" s="67"/>
       <c r="H32" s="66"/>
       <c r="I32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J32" s="66"/>
       <c r="K32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M32" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.55000000000000004">
@@ -4231,10 +4260,10 @@
         <v>406.1</v>
       </c>
       <c r="B33" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C33" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D33" s="65"/>
       <c r="E33" s="66"/>
@@ -4252,31 +4281,31 @@
         <v>407</v>
       </c>
       <c r="B34" s="64" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C34" s="64" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="D34" s="65"/>
       <c r="E34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G34" s="67"/>
       <c r="H34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J34" s="66"/>
       <c r="K34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L34" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M34" s="66"/>
     </row>
@@ -4285,10 +4314,10 @@
         <v>407.1</v>
       </c>
       <c r="B35" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C35" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D35" s="65"/>
       <c r="E35" s="66"/>
@@ -4306,15 +4335,15 @@
         <v>407.2</v>
       </c>
       <c r="B36" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C36" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D36" s="65"/>
       <c r="E36" s="65"/>
       <c r="F36" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="65"/>
@@ -4329,14 +4358,14 @@
         <v>407.3</v>
       </c>
       <c r="B37" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C37" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D37" s="65"/>
       <c r="E37" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F37" s="65"/>
       <c r="G37" s="68"/>
@@ -4352,10 +4381,10 @@
         <v>407.4</v>
       </c>
       <c r="B38" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C38" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D38" s="65"/>
       <c r="E38" s="65"/>
@@ -4365,10 +4394,10 @@
       <c r="I38" s="65"/>
       <c r="J38" s="65"/>
       <c r="K38" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L38" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M38" s="65"/>
     </row>
@@ -4377,27 +4406,27 @@
         <v>407.5</v>
       </c>
       <c r="B39" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C39" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D39" s="65"/>
       <c r="E39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G39" s="68"/>
       <c r="H39" s="65"/>
       <c r="I39" s="65"/>
       <c r="J39" s="65"/>
       <c r="K39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L39" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M39" s="65"/>
     </row>
@@ -4406,10 +4435,10 @@
         <v>407.6</v>
       </c>
       <c r="B40" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="65"/>
@@ -4419,10 +4448,10 @@
       <c r="I40" s="65"/>
       <c r="J40" s="65"/>
       <c r="K40" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L40" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M40" s="65"/>
     </row>
@@ -4431,14 +4460,14 @@
         <v>407.7</v>
       </c>
       <c r="B41" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C41" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D41" s="65"/>
       <c r="E41" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F41" s="65"/>
       <c r="G41" s="68"/>
@@ -4454,10 +4483,10 @@
         <v>407.8</v>
       </c>
       <c r="B42" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C42" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D42" s="65"/>
       <c r="E42" s="65"/>
@@ -4467,10 +4496,10 @@
       <c r="I42" s="65"/>
       <c r="J42" s="65"/>
       <c r="K42" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L42" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M42" s="65"/>
     </row>
@@ -4479,10 +4508,10 @@
         <v>408</v>
       </c>
       <c r="B43" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C43" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D43" s="66"/>
       <c r="E43" s="66"/>
@@ -4492,10 +4521,10 @@
       <c r="I43" s="66"/>
       <c r="J43" s="66"/>
       <c r="K43" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L43" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M43" s="66"/>
     </row>
@@ -4504,10 +4533,10 @@
         <v>408.1</v>
       </c>
       <c r="B44" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C44" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D44" s="66"/>
       <c r="E44" s="66"/>
@@ -4525,10 +4554,10 @@
         <v>408.2</v>
       </c>
       <c r="B45" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="C45" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D45" s="66"/>
       <c r="E45" s="66"/>
@@ -4546,10 +4575,10 @@
         <v>408.3</v>
       </c>
       <c r="B46" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C46" s="64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D46" s="65"/>
       <c r="E46" s="65"/>
@@ -4567,14 +4596,14 @@
         <v>409</v>
       </c>
       <c r="B47" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C47" s="64" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D47" s="65"/>
       <c r="E47" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F47" s="66"/>
       <c r="G47" s="67"/>
@@ -4590,10 +4619,10 @@
         <v>409.1</v>
       </c>
       <c r="B48" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C48" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D48" s="65"/>
       <c r="E48" s="66"/>
@@ -4611,15 +4640,15 @@
         <v>410</v>
       </c>
       <c r="B49" s="64" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C49" s="64" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D49" s="65"/>
       <c r="E49" s="66"/>
       <c r="F49" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G49" s="67"/>
       <c r="H49" s="66"/>
@@ -4634,10 +4663,10 @@
         <v>410.1</v>
       </c>
       <c r="B50" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C50" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D50" s="65"/>
       <c r="E50" s="66"/>
@@ -4655,20 +4684,20 @@
         <v>411</v>
       </c>
       <c r="B51" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C51" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D51" s="65"/>
       <c r="E51" s="66"/>
       <c r="F51" s="66"/>
       <c r="G51" s="67"/>
       <c r="H51" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I51" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J51" s="66"/>
       <c r="K51" s="66"/>
@@ -4680,10 +4709,10 @@
         <v>411.1</v>
       </c>
       <c r="B52" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C52" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D52" s="65"/>
       <c r="E52" s="66"/>
@@ -4701,29 +4730,29 @@
         <v>412</v>
       </c>
       <c r="B53" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C53" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D53" s="65"/>
       <c r="E53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F53" s="66"/>
       <c r="G53" s="67"/>
       <c r="H53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J53" s="66"/>
       <c r="K53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L53" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M53" s="66"/>
     </row>
@@ -4732,10 +4761,10 @@
         <v>412.1</v>
       </c>
       <c r="B54" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C54" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D54" s="65"/>
       <c r="E54" s="66"/>
@@ -4753,10 +4782,10 @@
         <v>412.2</v>
       </c>
       <c r="B55" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C55" s="64" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D55" s="65"/>
       <c r="E55" s="65"/>
@@ -4764,7 +4793,7 @@
       <c r="G55" s="68"/>
       <c r="H55" s="65"/>
       <c r="I55" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J55" s="65"/>
       <c r="K55" s="65"/>
@@ -4776,10 +4805,10 @@
         <v>412.3</v>
       </c>
       <c r="B56" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C56" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="D56" s="65"/>
       <c r="E56" s="65"/>
@@ -4787,7 +4816,7 @@
       <c r="G56" s="68"/>
       <c r="H56" s="65"/>
       <c r="I56" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J56" s="65"/>
       <c r="K56" s="65"/>
@@ -4799,10 +4828,10 @@
         <v>412.4</v>
       </c>
       <c r="B57" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C57" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D57" s="65"/>
       <c r="E57" s="65"/>
@@ -4810,7 +4839,7 @@
       <c r="G57" s="68"/>
       <c r="H57" s="65"/>
       <c r="I57" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J57" s="65"/>
       <c r="K57" s="65"/>
@@ -4822,10 +4851,10 @@
         <v>412.5</v>
       </c>
       <c r="B58" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C58" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="D58" s="65"/>
       <c r="E58" s="65"/>
@@ -4843,24 +4872,24 @@
         <v>412.6</v>
       </c>
       <c r="B59" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C59" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D59" s="65"/>
       <c r="E59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G59" s="68"/>
       <c r="H59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I59" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J59" s="65"/>
       <c r="K59" s="65"/>
@@ -4872,17 +4901,17 @@
         <v>412.7</v>
       </c>
       <c r="B60" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C60" s="64" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D60" s="65"/>
       <c r="E60" s="65"/>
       <c r="F60" s="65"/>
       <c r="G60" s="68"/>
       <c r="H60" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I60" s="65"/>
       <c r="J60" s="65"/>
@@ -4895,20 +4924,20 @@
         <v>413</v>
       </c>
       <c r="B61" s="64" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C61" s="64" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D61" s="65"/>
       <c r="E61" s="66"/>
       <c r="F61" s="66"/>
       <c r="G61" s="67"/>
       <c r="H61" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I61" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J61" s="66"/>
       <c r="K61" s="66"/>
@@ -4920,10 +4949,10 @@
         <v>411.1</v>
       </c>
       <c r="B62" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C62" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D62" s="65"/>
       <c r="E62" s="66"/>
@@ -4941,14 +4970,14 @@
         <v>414</v>
       </c>
       <c r="B63" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C63" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D63" s="65"/>
       <c r="E63" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F63" s="66"/>
       <c r="G63" s="67"/>
@@ -4964,10 +4993,10 @@
         <v>412.1</v>
       </c>
       <c r="B64" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C64" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D64" s="65"/>
       <c r="E64" s="66"/>
@@ -4985,22 +5014,22 @@
         <v>415</v>
       </c>
       <c r="B65" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C65" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D65" s="65"/>
       <c r="E65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F65" s="66"/>
       <c r="G65" s="67"/>
       <c r="H65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I65" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J65" s="66"/>
       <c r="K65" s="66"/>
@@ -5012,10 +5041,10 @@
         <v>413.1</v>
       </c>
       <c r="B66" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C66" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D66" s="65"/>
       <c r="E66" s="66"/>
@@ -5033,31 +5062,31 @@
         <v>502</v>
       </c>
       <c r="B67" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C67" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D67" s="65"/>
       <c r="E67" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F67" s="66" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G67" s="67"/>
       <c r="H67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J67" s="66"/>
       <c r="K67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L67" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M67" s="66"/>
     </row>
@@ -5066,10 +5095,10 @@
         <v>502.1</v>
       </c>
       <c r="B68" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C68" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D68" s="65"/>
       <c r="E68" s="66"/>
@@ -5087,29 +5116,29 @@
         <v>502.2</v>
       </c>
       <c r="B69" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C69" s="64" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D69" s="65"/>
       <c r="E69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F69" s="65"/>
       <c r="G69" s="68"/>
       <c r="H69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J69" s="65"/>
       <c r="K69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L69" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M69" s="65"/>
     </row>
@@ -5118,14 +5147,14 @@
         <v>502.3</v>
       </c>
       <c r="B70" s="64" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C70" s="64" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D70" s="65"/>
       <c r="E70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F70" s="65"/>
       <c r="G70" s="68"/>
@@ -5133,10 +5162,10 @@
       <c r="I70" s="65"/>
       <c r="J70" s="65"/>
       <c r="K70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L70" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M70" s="65"/>
     </row>
@@ -5145,43 +5174,43 @@
         <v>502.4</v>
       </c>
       <c r="B71" s="64" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C71" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D71" s="65"/>
       <c r="E71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G71" s="68"/>
       <c r="H71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J71" s="65"/>
       <c r="K71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L71" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M71" s="65"/>
     </row>
     <row r="72" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="65" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B72" s="64" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C72" s="64" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D72" s="65"/>
       <c r="E72" s="65"/>
@@ -5191,22 +5220,22 @@
       <c r="I72" s="65"/>
       <c r="J72" s="65"/>
       <c r="K72" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L72" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M72" s="65"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="65" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B73" s="64" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C73" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D73" s="65"/>
       <c r="E73" s="65"/>
@@ -5216,22 +5245,22 @@
       <c r="I73" s="65"/>
       <c r="J73" s="65"/>
       <c r="K73" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L73" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M73" s="65"/>
     </row>
     <row r="74" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="65" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B74" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C74" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="D74" s="65"/>
       <c r="E74" s="65"/>
@@ -5241,32 +5270,32 @@
       <c r="I74" s="65"/>
       <c r="J74" s="65"/>
       <c r="K74" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L74" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M74" s="65"/>
     </row>
     <row r="75" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="65" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B75" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C75" s="64" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D75" s="65"/>
       <c r="E75" s="65"/>
       <c r="F75" s="65"/>
       <c r="G75" s="68"/>
       <c r="H75" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I75" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J75" s="65"/>
       <c r="K75" s="65"/>
@@ -5275,23 +5304,23 @@
     </row>
     <row r="76" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="65" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B76" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C76" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D76" s="65"/>
       <c r="E76" s="65"/>
       <c r="F76" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G76" s="68"/>
       <c r="H76" s="65"/>
       <c r="I76" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J76" s="65"/>
       <c r="K76" s="65"/>
@@ -5300,26 +5329,26 @@
     </row>
     <row r="77" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="65" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B77" s="64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C77" s="64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D77" s="65"/>
       <c r="E77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G77" s="68"/>
       <c r="H77" s="65"/>
       <c r="I77" s="65"/>
       <c r="J77" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K77" s="65"/>
       <c r="L77" s="65"/>
@@ -5327,23 +5356,23 @@
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="65" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B78" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C78" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D78" s="65"/>
       <c r="E78" s="65"/>
       <c r="F78" s="65"/>
       <c r="G78" s="68"/>
       <c r="H78" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I78" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J78" s="65"/>
       <c r="K78" s="65"/>
@@ -5355,31 +5384,31 @@
         <v>503</v>
       </c>
       <c r="B79" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C79" s="64" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D79" s="65"/>
       <c r="E79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G79" s="67"/>
       <c r="H79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J79" s="66"/>
       <c r="K79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L79" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M79" s="66"/>
     </row>
@@ -5388,10 +5417,10 @@
         <v>503.1</v>
       </c>
       <c r="B80" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C80" s="64" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D80" s="65"/>
       <c r="E80" s="66"/>
@@ -5409,15 +5438,15 @@
         <v>503.2</v>
       </c>
       <c r="B81" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C81" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D81" s="65"/>
       <c r="E81" s="65"/>
       <c r="F81" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G81" s="68"/>
       <c r="H81" s="65"/>
@@ -5432,14 +5461,14 @@
         <v>503.3</v>
       </c>
       <c r="B82" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C82" s="64" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="D82" s="65"/>
       <c r="E82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F82" s="65"/>
       <c r="G82" s="68"/>
@@ -5447,10 +5476,10 @@
       <c r="I82" s="65"/>
       <c r="J82" s="65"/>
       <c r="K82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L82" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M82" s="65"/>
     </row>
@@ -5459,22 +5488,22 @@
         <v>503.4</v>
       </c>
       <c r="B83" s="64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C83" s="64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D83" s="65"/>
       <c r="E83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F83" s="65"/>
       <c r="G83" s="68"/>
       <c r="H83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I83" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J83" s="65"/>
       <c r="K83" s="65"/>
@@ -5486,24 +5515,24 @@
         <v>504</v>
       </c>
       <c r="B84" s="64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C84" s="64" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D84" s="65"/>
       <c r="E84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G84" s="67"/>
       <c r="H84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I84" s="66" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J84" s="66"/>
       <c r="K84" s="66"/>
@@ -5515,10 +5544,10 @@
         <v>504.1</v>
       </c>
       <c r="B85" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C85" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="D85" s="65"/>
       <c r="E85" s="66"/>
@@ -5536,24 +5565,24 @@
         <v>504.2</v>
       </c>
       <c r="B86" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C86" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="D86" s="65"/>
       <c r="E86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G86" s="68"/>
       <c r="H86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I86" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J86" s="65"/>
       <c r="K86" s="65"/>
@@ -5562,25 +5591,25 @@
     </row>
     <row r="87" spans="1:13" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="65" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B87" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C87" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D87" s="65"/>
       <c r="E87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F87" s="65"/>
       <c r="G87" s="68"/>
       <c r="H87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I87" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J87" s="65"/>
       <c r="K87" s="65"/>
@@ -5589,20 +5618,20 @@
     </row>
     <row r="88" spans="1:13" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="65" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B88" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C88" s="64" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="D88" s="65"/>
       <c r="E88" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F88" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G88" s="68"/>
       <c r="H88" s="65"/>
@@ -5617,24 +5646,24 @@
         <v>504.3</v>
       </c>
       <c r="B89" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C89" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D89" s="65"/>
       <c r="E89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G89" s="68"/>
       <c r="H89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I89" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J89" s="65"/>
       <c r="K89" s="65"/>
@@ -5646,24 +5675,24 @@
         <v>504.4</v>
       </c>
       <c r="B90" s="64" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C90" s="64" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D90" s="65"/>
       <c r="E90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G90" s="68"/>
       <c r="H90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="I90" s="65" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J90" s="65"/>
       <c r="K90" s="65"/>

--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1CE2EF9B-D880-4828-96BF-6BC2894FD664}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B9A62C6-BB14-491F-9E68-379A1161B026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="1110" windowWidth="11960" windowHeight="13930" xr2:uid="{0C676DF9-F0DB-49D1-BDB4-25666544DF64}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{2CEA763C-E0EF-4484-95F1-373373058285}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -2628,7 +2628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A979893C-E8DE-439D-9E11-08A170BA34C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB75B205-105C-43E6-B5BA-D9EC4324865B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3444,7 +3444,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{4CC28AF9-C221-4F11-8B9B-ADCE71E42F59}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{D5B09897-9A54-4CD0-B52A-16E1F0515EBB}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3452,7 +3452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{614CED36-19BF-4F04-8083-5FCF41145834}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C81607-BE63-4E64-B33E-204F4993E8C8}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B9A62C6-BB14-491F-9E68-379A1161B026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C74D25B8-761E-4D1A-80BC-A70A02A4C429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{2CEA763C-E0EF-4484-95F1-373373058285}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{01CDD4B0-1E31-475E-8DB7-072A9741DEDE}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2025</t>
+      <t>2024</t>
     </r>
     <r>
       <rPr>
@@ -2628,7 +2628,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB75B205-105C-43E6-B5BA-D9EC4324865B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2505D6B-F887-41C4-9490-C81068506B3B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3444,7 +3444,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{D5B09897-9A54-4CD0-B52A-16E1F0515EBB}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{F0E6280A-7A33-4C1E-810F-C72F740FC849}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3452,7 +3452,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8C81607-BE63-4E64-B33E-204F4993E8C8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E289D8C-5B48-4808-A13D-470A571B006C}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>

--- a/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
+++ b/file/Intune_Company_Portal_Web_VPATJ07180.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C74D25B8-761E-4D1A-80BC-A70A02A4C429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{318CFD59-350C-451E-B23A-D54594D07C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{01CDD4B0-1E31-475E-8DB7-072A9741DEDE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{E24FD681-6493-4EEC-8886-E70058CA2737}"/>
   </bookViews>
   <sheets>
     <sheet name="情報アクセシビリティ自己評価様式" sheetId="2" r:id="rId1"/>
@@ -73,7 +73,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>2024</t>
+      <t>2025</t>
     </r>
     <r>
       <rPr>
@@ -192,7 +192,6 @@
   </si>
   <si>
     <t>Intune Company Portal(Web)</t>
-    <phoneticPr fontId="4"/>
   </si>
   <si>
     <r>
@@ -1717,7 +1716,7 @@
     </font>
     <font>
       <b/>
-      <sz val="28"/>
+      <sz val="36"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -2628,8 +2627,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2505D6B-F887-41C4-9490-C81068506B3B}">
-  <sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F410980-F835-4706-BBDD-6A56B2E6CB56}">
+  <sheetPr codeName="Sheet241">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I54"/>
@@ -3444,7 +3443,7 @@
   </mergeCells>
   <phoneticPr fontId="4"/>
   <hyperlinks>
-    <hyperlink ref="B14" r:id="rId1" xr:uid="{F0E6280A-7A33-4C1E-810F-C72F740FC849}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{922ED857-FD30-4F91-8AB0-81FD80818EA1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="25" orientation="portrait" r:id="rId2"/>
@@ -3452,7 +3451,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E289D8C-5B48-4808-A13D-470A571B006C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D50B47BF-2C79-4C9F-A45A-F97197579321}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:M90"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
